--- a/output/exports/setup_summary.xlsx
+++ b/output/exports/setup_summary.xlsx
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>499</v>
+        <v>487</v>
       </c>
     </row>
     <row r="6">
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
   </sheetData>

--- a/output/exports/setup_summary.xlsx
+++ b/output/exports/setup_summary.xlsx
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>204</v>
+        <v>620</v>
       </c>
     </row>
   </sheetData>
